--- a/Classification/Neuronorma data TMT, SDMT, DS, SF.xlsx
+++ b/Classification/Neuronorma data TMT, SDMT, DS, SF.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rachelmorse/Documents/2023:2024/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rachelmorse/superagers/Classification/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C866FAD-CE3B-BB40-9A19-7B0E511AC9EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BAF5C11-4059-6D4A-978E-E698EEDF7E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="520" windowWidth="19420" windowHeight="16240" xr2:uid="{BAA7F087-5EAE-0840-BB6F-5BE235FE3022}"/>
+    <workbookView xWindow="12940" yWindow="22100" windowWidth="28800" windowHeight="16240" xr2:uid="{BAA7F087-5EAE-0840-BB6F-5BE235FE3022}"/>
   </bookViews>
   <sheets>
     <sheet name="60-62" sheetId="1" r:id="rId1"/>
@@ -1086,7 +1086,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1114,12 +1114,6 @@
       <sz val="12"/>
       <color rgb="FFD1F1A9"/>
       <name val="Menlo"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
